--- a/www/download/COUNTRY.HRV.EXI382.xlsx
+++ b/www/download/COUNTRY.HRV.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>Croácia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910323926380368</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910630674846626</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910630674846626</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910630674846626</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910630674846626</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910630674846626</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910630674846626</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910630674846626</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.910630674846626</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1.824</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.548</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.557</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.566</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1.601</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.508</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.611</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.525</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.559</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.588</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1.638</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.629</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.634</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.673</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.634</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.605</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.491</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.444</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1.448</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>1.435</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1.432</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>1.528</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1.629</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>1.656</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1.731</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1.422</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.078</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1.172</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.241</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.165</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.193</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.211</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.256</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.237</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.268</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.325</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.281</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.258</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.192</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.153</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.137</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1.149</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1.154</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1.141</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>1.209</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1.185</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>1.289</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>1.307</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1.372</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3636.732</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3275.633</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3301.569</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>3314.102</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3413.668</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3213.14</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3441.038</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3255.942</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3328.591</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3382.951</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3469.005</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3409.757</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>3415.917</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3500.428</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3391.451</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3308.779</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3157.4</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3041.67</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2938.848</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2951.8</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>2925.911</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2913.721</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>3101.362</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>3064.751</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>3293.188</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>3344.912</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3482.664</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2947.64</t>
+          <t>6906964752.3979</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1412.625</t>
+          <t>6658619899.3585</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1560.016</t>
+          <t>7218379559.08998</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1719.726</t>
+          <t>7418234440.06785</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1891.816</t>
+          <t>6924451401.44217</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1737.141</t>
+          <t>6443132669.1144</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1949.962</t>
+          <t>6668515971.60236</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1810.398</t>
+          <t>6359007108.81624</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1860.698</t>
+          <t>6428507610.00415</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1902.033</t>
+          <t>6946556140.92706</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1991.303</t>
+          <t>7127478737.63477</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1968.565</t>
+          <t>7521299932.01898</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2745.376</t>
+          <t>7078536440.02292</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2862.115</t>
+          <t>7406337146.5082</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2756.43</t>
+          <t>7075777830.42661</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2070.397</t>
+          <t>6884928924.41991</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2220.584</t>
+          <t>6691763417.311</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1859.314</t>
+          <t>6217607700.72785</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1844.23</t>
+          <t>5885604989.18536</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2415.338</t>
+          <t>5553697344.83765</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2421.573</t>
+          <t>5236775199.74179</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2395.935</t>
+          <t>5380798121.13387</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2536.844</t>
+          <t>6242065375.85531</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2480.128</t>
+          <t>8161803922.91668</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2693.562</t>
+          <t>6747540049.07491</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2729.255</t>
+          <t>7000469918.89596</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2854.372</t>
+          <t>6401659917.53015</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1512114403.21384</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1944008201.06363</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2322599107.94042</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2740162196.09041</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2648233165.95015</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2618996057.12868</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2266613804.7719</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1657566292.84036</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1640599048.5725</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1883091955.46909</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2118477591.32856</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2044293786.65497</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1863010983.75056</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1935231283.17131</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2133655722.21812</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2100242371.8062</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1722445463.64578</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1557883691.96608</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1508932358.9699</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1611319130.26728</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1411365269.12703</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1426226749.86269</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1490875004.86021</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1572249620.81895</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1658640173.36497</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1809601915.68275</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1397471778.94419</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>121928205.745403</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>263177640.514517</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>39088603.787012</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>36813547.2872088</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>33389475.0654976</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2973582423.06383</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30154655.9206691</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30556879.2895058</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>28895411.9919259</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>26224444.9449791</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1556724897.91402</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>33718753.883431</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>20747027.638598</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>22672799.238522</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>20944633.3206855</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>21298503.2771584</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>20458404.2133657</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>19177809.3768537</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>21817794.6916169</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>107627474.161406</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>105029766.292524</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>104219069.032898</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>49543840.1101356</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>61910540.2766158</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>54399930.0288436</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>51115042.9672657</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>49002720.7752324</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6893.17988693454</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16341.8204580601</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>17736.2515730306</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>19293.3693141263</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>19781.6118253618</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>22112.8895796762</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>23124.4675619291</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>21601.8887876932</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>20443.6468981525</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>20197.2587729895</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>22442.0758693705</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>23321.0011138066</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>23331.0927030154</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>24363.8709708707</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>23334.7035113537</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>26056.8138641446</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>25883.4105784514</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>27707.0199432417</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>25969.6528002534</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>25381.4288898313</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>28302.623078304</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>25562.817606079</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>28221.6303930077</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>28062.3163014193</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>30652.3434554873</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>29217.8829533982</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>29756.7576607712</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>25746.4200560379</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>50599.3348965838</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>59743.8136359422</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>63121.3193296047</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>62148.9929781847</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>69127.1685661839</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>71838.2653161222</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>66404.8010715321</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>61667.2692033638</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>65119.9472424366</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>71629.5346557574</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>80856.3051305769</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>78840.1170146508</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>82888.0927477338</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>79355.9033819058</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>89045.2625361384</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>90099.9822450945</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>92402.0387046183</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>85441.2054948226</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>83451.1827372859</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>88889.7927737773</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>83248.6832863832</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>102102.029189441</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>129841.68794618</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>114369.931620259</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>112878.776322078</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>101342.502621845</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.949349837128722</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.273344114892844</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.328331783704827</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.372399924918943</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.285630878608316</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.336714923541021</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.139702583697664</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.0922024704658098</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.134157673453583</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0100584809342814</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.060031124165728</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.0370439841617629</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.473623088615564</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.47895242542276</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.291881333664567</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.0142104417122264</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.289203978112716</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.193487042445581</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.222208529784016</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.498981680287753</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.715766269526858</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.679911673488712</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.701580861541585</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.577438948275506</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.62395807345223</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.508207412489205</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.04252599068093</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1063.43574580007</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1803.34712529125</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2074.49009283706</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2338.02235161367</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2170.86086232548</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2296.35778792534</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1826.0000038441</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1422.43739195067</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1374.7268716047</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1554.60410754452</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1686.95460370183</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1651.95457507511</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1468.67243496301</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1460.99296630818</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1665.09733277497</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1669.77450453628</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1444.76217383494</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1351.39112765995</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1327.23402143509</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1402.60369278238</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1223.07908292525</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1249.83674972658</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1232.72344005696</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1326.83714866508</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1286.97075734903</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1384.92327484813</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1018.8311081489</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-128288960.851841</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-119907427.467606</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>700631223.019132</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>392407831.283569</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>526849593.944773</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>393512952.583848</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>217450127.72156</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>357362152.920744</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>460421147.597848</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>613658841.599769</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>729382085.796494</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>774344186.446856</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>425221181.698665</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>305392140.617982</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>481364506.084656</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>561397474.387087</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>528692589.867331</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>613186061.444609</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>336823075.331634</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>319951723.451007</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>253163156.312016</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>403699818.421995</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>226907179.946794</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>34886274.9861802</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>515750025.145549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>601414107.642133</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>-196737415.984336</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>30288014.5559111</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-185957599.821089</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>654531283.309814</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>325853029.681854</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>463015904.679849</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>309068959.165609</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>24698953.336006</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>165945915.312604</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-10498979.1694424</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>145744217.880636</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>211676976.630296</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>184257715.002213</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>33898671.0993738</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-25570526.8187523</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>124151781.684629</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>188105857.373532</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>231044618.199687</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>315752590.879212</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>52409589.2345646</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>41404188.6362429</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-63002448.4240096</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>34196904.5538258</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-155661484.743074</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-370771029.649054</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>48849704.5185049</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>75332046.7654229</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>224652144.693129</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-158576975.407752</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>66050172.3534829</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>46099939.7093184</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>66554801.6017145</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>63833689.2649243</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>84443993.4182389</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>192751174.385554</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>191416237.60814</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>470920126.767291</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>467914623.719133</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>517705109.166198</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>590086471.444643</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>391322510.599291</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>330962667.436734</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>357212724.400027</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>373291617.013555</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>297647971.667645</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>297433470.565398</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>284413486.09707</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>278547534.814764</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>316165604.736026</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>369502913.86817</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>382568664.689868</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>405657304.635234</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>466900320.627044</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>526082060.87671</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-421389560.677465</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2073.00829787223</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1310.41280148396</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>1393.36906037787</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1467.34300341393</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>1550.79596688305</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>1523.13985094123</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1570.90308547513</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1553.58963357146</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1559.15703033331</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1570.24106332061</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>1585.68482242506</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>1590.75959596007</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>2164.26960977473</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2160.73909104708</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>2151.10816294664</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1646.046271267</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1862.59314193478</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1612.86780013807</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1622.1567420175</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>2102.47724018474</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>2098.51783544698</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>2099.61534582087</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>2097.57861317463</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>2093.00459632312</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>2089.9865516939</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>2088.75154885478</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>2080.98901850839</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1993.82071427138</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2116.45215480995</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2121.01310548628</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2116.14967115826</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2132.4762618691</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2130.44689033258</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2135.96399751705</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>2135.18394648843</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2134.94387787848</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2130.1876456147</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>2117.44186046546</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>2092.5173366065</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>2091.16437098223</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>2092.431107658</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2075.80548414721</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>2061.92995575448</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>2050.6592193283</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>2040.15695217639</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>2035.91825424253</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>2038.64510482174</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>2038.34672105056</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2034.78069674241</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>2029.86096882719</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>2016.87911301343</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2021.41101249619</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>2019.42307805215</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>2012.03026332406</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4864.3289049504</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5883.54465486625</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>6440.26473101517</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6682.61774652964</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>6942.82812637959</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>8990.41958022401</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10461.1807555568</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>10793.4055590079</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>10886.8744616421</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>11988.4723056175</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>12976.9625061116</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>14887.1626706326</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>15362.6704186608</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>15380.6668463658</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>14219.0569569093</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>16675.9165202563</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>17694.410237916</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>18181.9737465627</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>18552.7708990214</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>19521.6611955686</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>22329.4502417935</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>24019.5103642025</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>26469.8053017998</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>27614.3977548243</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>29603.7579072642</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>31461.1831574718</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>29948.2095113823</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>967189782.274818</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>976343079.364048</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1030045154.09964</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1265917007.67396</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1207473587.28619</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1194043328.77214</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1320370317.26201</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1231315441.5199</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>980883575.324784</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1079025737.70053</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1057164824.97568</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1301187153.3684</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1237428308.58904</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1292589371.27998</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1278323617.65188</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1574434885.9713</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1651678656.68876</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1582678311.49496</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1585404737.14615</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1526419814.45727</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>1609727430.27236</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1730471332.42723</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2088985987.91602</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2468361958.85788</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2187313403.76969</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2398058623.13441</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2109393297.16241</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>6718.56134126003</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7476.24515126397</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>9987.1923391702</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8697.90861268011</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>8680.1611726037</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>10380.838704043</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12223.933196059</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>14322.1388327795</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>15085.2990616275</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>15752.588727678</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>17169.0292048816</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>19373.9114408273</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>20194.0166906516</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>21775.9149818125</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>17514.8236941089</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>17671.7097453321</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>18867.0402153221</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>19161.3408589474</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>19784.3666242784</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>19737.6344503816</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>22201.185044734</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>23338.1508986219</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>26072.7756592731</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>28184.9353277434</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>29998.6386502281</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>32261.4255218832</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>31318.4437469586</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3636.732</t>
+          <t>1889372151.09226</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3275.633</t>
+          <t>1179973723.0844</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3301.569</t>
+          <t>2394617659.11553</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3314.102</t>
+          <t>2038002253.51268</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3413.668</t>
+          <t>2053026318.41816</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3213.14</t>
+          <t>1803266708.41724</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3441.038</t>
+          <t>1822115375.66615</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3255.942</t>
+          <t>2179153062.78368</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3328.591</t>
+          <t>2154523257.45187</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3382.951</t>
+          <t>2382985293.89294</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3469.005</t>
+          <t>2487672515.6361</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3409.757</t>
+          <t>2743122314.98426</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3415.917</t>
+          <t>2262617684.98717</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3500.428</t>
+          <t>2474382155.93272</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3391.451</t>
+          <t>2244796676.7645</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3308.779</t>
+          <t>2258615672.9125</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3157.4</t>
+          <t>2315593958.09628</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3041.67</t>
+          <t>2302645975.3375</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2938.848</t>
+          <t>2063311483.35559</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2951.8</t>
+          <t>1869330810.72093</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2925.911</t>
+          <t>1850491846.26606</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2913.721</t>
+          <t>2061908529.06083</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>3101.362</t>
+          <t>2277650178.07476</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>3064.751</t>
+          <t>2559953795.56682</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>3293.188</t>
+          <t>2739103170.04344</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>3344.912</t>
+          <t>3077129311.28224</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3482.664</t>
+          <t>2046164755.29949</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2947.64</t>
+          <t>-1854.23243630963</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1412.625</t>
+          <t>-1592.70049639772</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1560.016</t>
+          <t>-3546.92760815502</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1719.726</t>
+          <t>-2015.29086615047</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1891.816</t>
+          <t>-1737.33304622411</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1737.141</t>
+          <t>-1390.41912381899</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1949.962</t>
+          <t>-1762.75244050218</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1810.398</t>
+          <t>-3528.73327377165</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1860.698</t>
+          <t>-4198.42459998541</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1902.033</t>
+          <t>-3764.11642206049</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1991.303</t>
+          <t>-4192.06669876998</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1968.565</t>
+          <t>-4486.74877019471</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2745.376</t>
+          <t>-4831.34627199078</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2862.115</t>
+          <t>-6395.2481354467</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2756.43</t>
+          <t>-3295.76673719967</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2070.397</t>
+          <t>-995.793225075803</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2220.584</t>
+          <t>-1172.6299774061</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1859.314</t>
+          <t>-979.367112384753</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1844.23</t>
+          <t>-1231.59572525698</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2415.338</t>
+          <t>-215.973254812969</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2421.573</t>
+          <t>128.265197059505</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2395.935</t>
+          <t>681.359465580623</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2536.844</t>
+          <t>397.029642526674</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>2480.128</t>
+          <t>-570.537572919044</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2693.562</t>
+          <t>-394.880742963894</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2729.255</t>
+          <t>-800.242364411459</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2854.372</t>
+          <t>-1370.2342355763</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3602.459</t>
+          <t>-922182368.817441</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3583.269</t>
+          <t>-203630643.720348</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3919.182</t>
+          <t>-1364572505.01589</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4005.595</t>
+          <t>-772085245.838724</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3819.02</t>
+          <t>-845552731.13197</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3582.574</t>
+          <t>-609223379.645096</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3738.6</t>
+          <t>-501745058.404144</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3644.827</t>
+          <t>-947837621.263775</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3603.566</t>
+          <t>-1173639682.12708</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3888.546</t>
+          <t>-1303959556.19241</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3969.725</t>
+          <t>-1430507690.66043</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>4130.557</t>
+          <t>-1441935161.61586</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3899.878</t>
+          <t>-1025189376.39813</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>4096.735</t>
+          <t>-1181792784.65273</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3851.749</t>
+          <t>-966473059.112619</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>3800.167</t>
+          <t>-684180786.941207</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>3701.164</t>
+          <t>-663915301.407523</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>3462.522</t>
+          <t>-719967663.842542</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>3278.995</t>
+          <t>-477906746.209435</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>3080.405</t>
+          <t>-342910996.263655</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2961.008</t>
+          <t>-240764415.993697</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2994.651</t>
+          <t>-331437196.633602</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>3302.737</t>
+          <t>-188664190.158743</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3558.938</t>
+          <t>-91591836.7089337</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>3564.317</t>
+          <t>-551789766.273747</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>3704.886</t>
+          <t>-679070688.147831</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>3393.383</t>
+          <t>63228541.862915</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>6183.27161390022</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>5534.18029984992</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>8228.48461582968</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>7853.59191405904</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>7531.21303955822</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>8470.58384351775</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>9113.10765298939</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>9100.36508129676</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>9572.01347217178</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>10842.5967538197</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>11750.2896970112</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>13149.2955389153</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>14522.1112974022</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>15980.9977751453</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>15785.1760606168</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>15642.9379144511</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>14648.4273229942</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>14325.2658827617</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>14297.191922719</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>15173.1697993508</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>14999.3429478211</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>15874.9672055211</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>16571.064198688</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>16613.749506106</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>17453.8562549262</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>18475.206130067</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>19641.3296535976</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1849.226</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2150.502</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2142.933</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2267.423</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2204.007</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2061.075</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2146.57</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2068.624</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2131.149</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2154.507</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2233.093</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2169.333</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2094.746</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2176.996</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>2080.641</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2014.698</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>1922.372</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1864.368</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1788.916</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1689.141</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>1667.396</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1652.259</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>1725.345</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>1763.988</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>1808.412</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>1812.023</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1879.692</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8810.67401141436</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>9089.12465309813</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>10353.763058383</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>12455.5264042534</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>11944.3227066933</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>13234.3259587683</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>14663.727208711</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>14057.6991093612</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>14867.116319006</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17066.0871160631</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>18625.6354199853</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20365.3668044781</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22875.3700304322</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>24628.0922674143</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>23976.9405893918</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>24645.984494581</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22999.189922054</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>21917.7046384386</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22432.6929545626</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>23396.5646471618</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23514.558127687</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24487.7718891614</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>25909.7981529896</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>26122.3238092254</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>27684.64605867</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27218.5135733675</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>27371.3425298287</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1233.899</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1484.456</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1954.569</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2185.414</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2127.164</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2124.139</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1896.017</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>1475.173</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>1470.648</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1683.009</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1887.384</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1819.381</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1632.482</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>1695.553</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1837.089</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1824.548</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>1517.61</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1391.313</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1362.635</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>1478.818</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>1298.266</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1332.491</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>1353.706</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>1374.669</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>1558.82</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>1699.3</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1275.622</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>138.89</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-4.84</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-20.19</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-21.31</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-11.06</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-18.22</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>22.72</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>26.52</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>13.01</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>5.51</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>68.17</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>68.8</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>50.04</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>13.47</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>46.32</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>35.34</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>63.33</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>86.52</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>79.81</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>80.42</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>72.79</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>60.61</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>123.76</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>96.571</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>229.281</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>28.294</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>26.215</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>24.076</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2657.649</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>22.48</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>22.232</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>21.043</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>1390.233</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>23.304</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>14.956</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>16.384</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>14.83</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>14.823</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>14.515</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>13.718</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>16.147</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>92.809</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>90.774</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>89.787</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>39.736</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>49.812</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>44.97</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>42.03</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>40.521</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5930.96028994034</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>6999.03454773446</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>7698.17365656863</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7390.10471751438</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>7280.89741186088</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>7341.64686083327</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8169.01323957822</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11103.6756782617</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>12219.8208807028</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>12566.8167097163</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>13501.8367337382</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>15191.4337805609</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>15935.4099540295</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>17413.1187045758</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>15507.8076192871</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>15227.1473612751</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>16298.735970055</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>16443.9690468387</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>15783.3484038791</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>14527.0695559008</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>15423.2743553881</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>15956.5514166134</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>16606.8618268772</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18658.5981531424</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>19249.6827611459</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>20665.6351754147</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>22037.4451266692</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2947639965.6249</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1412624999.99946</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1560015999.9991</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1719726000.00062</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1891816000.00013</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1737140999.99836</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1949962000.00048</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1810398000.00109</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1860697999.99915</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1902033000.00068</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1991303000.0012</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1968565000.00013</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2745375999.99923</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2862115000.0002</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2756430000.00017</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2070397000.0001</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2220583543.81434</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1859313999.9988</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1844230000.00013</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2415337857.36785</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2421572922.74985</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>2395934966.1362</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2536844375.22084</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>2480127788.29121</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2693562100.48825</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>2729255022.88739</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2854372429.73663</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3636731513.05804</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3275632999.99976</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3301568999.99992</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3314102000.00005</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3413667999.99969</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3213139999.99928</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3441038000.00016</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3255942000.0004</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3328590999.99974</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3382951000.00155</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3469005000.00029</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3409756999.99995</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3415916999.99948</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3500428000.00041</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3391451000.00007</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>3308778999.99975</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3157399999.99946</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3041669999.99932</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2938847999.99973</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2951799566.27507</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>2925910662.16328</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2913721492.70831</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>3101361865.74348</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>3064751073.24278</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>3293187605.81069</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>3344911924.98342</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>3482664249.46225</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1849226044.14005</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2150502000.00019</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2142933100.81933</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2267423086.70145</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2204006906.03294</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2061075033.37015</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2146570224.00174</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2068623987.24492</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2131149009.17069</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2154507150.27565</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2233093085.9184</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2169332914.8373</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2094745621.10503</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2176995954.69611</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2080641398.41753</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2014697990.01005</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1922371744.23585</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1864367745.3267</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1788915748.59445</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1689140520.3615</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>1667395884.26429</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>1652258696.66309</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>1725345356.25661</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>1763987567.45977</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1808411635.24193</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>1812022750.18887</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1879691519.98774</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1824001.26903438</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1547700.00000019</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1556599.99999999</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1566099.99999958</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1600799.99999983</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1508199.99999985</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1611000.00000009</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1524900.00000009</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1559099.99999972</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1588100.0000004</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1638299.99999987</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1629499.99999984</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1633500</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1672899.99999969</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1633800.00000017</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1604700.00000026</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1539699.99999985</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1490899.99999977</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1443500.00000031</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1447922.22996223</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>1435433.25183425</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>1431958.48937089</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>1527869.10698391</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>1519551.1984175</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1629152.8963939</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>1656370.06001228</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1730920.41056508</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1421914.21455013</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1077999.99999981</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1119600.00000002</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1171999.99999966</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1219899.99999967</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1140499.99999993</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1241300.00000012</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1165300.00000017</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1193399.9999996</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1211300.00000026</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1255799.99999988</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1237499.99999971</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1268499.99999999</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1324599.99999965</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1281400.00000016</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1257800.00000028</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1192199.99999983</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1152799.99999977</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1136900.00000027</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1148805.70938101</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>1153944.40868979</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>1141130.43177415</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>1209415.63729113</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>1184960.50732434</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>1288793.98688244</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>1306644.16473266</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1371642.23566283</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3636731513.05804</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3275632999.99976</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3301568999.99992</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3314102000.00005</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3413667999.99969</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3213139999.99928</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3441038000.00016</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3255942000.0004</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3328590999.99974</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3382951000.00155</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3469005000.00029</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3409756999.99995</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3415916999.99948</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3500428000.00041</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3391451000.00007</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3308778999.99975</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3157399999.99946</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3041669999.99932</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2938847999.99973</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2951799566.27507</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>2925910662.16328</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2913721492.70831</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>3101361865.74348</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>3064751073.24278</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>3293187605.81069</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>3344911924.98342</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3482664249.46225</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2947639965.6249</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1412624999.99946</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1560015999.9991</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1719726000.00062</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1891816000.00013</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1737140999.99836</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1949962000.00048</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1810398000.00109</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1860697999.99915</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1902033000.00068</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1991303000.0012</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1968565000.00013</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2745375999.99923</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2862115000.0002</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2756430000.00017</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2070397000.0001</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2220583543.81434</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1859313999.9988</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1844230000.00013</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2415337857.36785</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>2421572922.74985</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2395934966.1362</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2536844375.22084</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>2480127788.29121</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2693562100.48825</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>2729255022.88739</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2854372429.73663</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>27796.6688905518</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>30411.6215540897</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>32955.6274767367</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>34576.4740725393</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>32954.6465364767</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>34893.5201123783</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>38590.6986002465</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>41919.3758104968</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>44675.1363082375</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>49990.619048459</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>56509.215230515</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>61232.963378637</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>67608.2351785124</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>73366.06319877</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>67762.6672202753</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>67654.8084629261</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>67607.8071154426</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>66938.3593954041</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>66096.0896974016</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>67045.3629290227</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>67788.8167241964</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>71951.1921056565</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>75899.6707428583</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>80797.2550770953</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>82386.0000059252</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>85402.5979303745</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>89938.5145893579</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>9899.45809802025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>10272.374094164</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>11741.5407041449</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>13621.9130440204</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>13041.9288680172</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>14374.8374379604</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15794.7994521949</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>15165.3059844997</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>16210.8110504593</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>18414.4546374208</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>20306.6265315877</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>22043.1426313111</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>24784.9265945763</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>26888.8734107661</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>26116.2311041288</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>26652.186095027</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>25286.9206351369</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>24376.4015583748</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>24804.1074921639</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>25766.4844722728</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>26032.8185224329</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>27334.3121315087</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>28884.5575778023</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>29329.9542193498</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>30922.5204909022</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>30857.038153446</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>30787.7571581331</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
